--- a/Source/SmartInventory/SmartInventory/Content/Templates/Bulk/FiberData.xlsx
+++ b/Source/SmartInventory/SmartInventory/Content/Templates/Bulk/FiberData.xlsx
@@ -4,18 +4,31 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7990"/>
+    <workbookView windowWidth="19035" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>link_type</t>
   </si>
@@ -57,6 +70,9 @@
   </si>
   <si>
     <t>each_lmc_length</t>
+  </si>
+  <si>
+    <t>link_prefix</t>
   </si>
   <si>
     <t>Main Link</t>
@@ -113,21 +129,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,55 +173,50 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -224,27 +228,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -257,6 +268,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -264,51 +290,34 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,43 +356,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,31 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,91 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -557,16 +560,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -580,17 +583,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,17 +637,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,171 +656,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -807,76 +810,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1147,25 +1150,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N14"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="9.27272727272727" customWidth="1"/>
-    <col min="3" max="3" width="15.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="12.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="14.5454545454545" customWidth="1"/>
-    <col min="6" max="6" width="17.6363636363636" customWidth="1"/>
-    <col min="7" max="7" width="20.0909090909091" customWidth="1"/>
-    <col min="8" max="8" width="16.0909090909091" customWidth="1"/>
-    <col min="9" max="9" width="22.6363636363636" customWidth="1"/>
-    <col min="10" max="10" width="15.3636363636364" customWidth="1"/>
-    <col min="11" max="11" width="21.9090909090909" customWidth="1"/>
-    <col min="12" max="12" width="18.7272727272727" customWidth="1"/>
-    <col min="13" max="13" width="16.2727272727273" customWidth="1"/>
+    <col min="2" max="2" width="9.27619047619048" customWidth="1"/>
+    <col min="3" max="3" width="15.5428571428571" customWidth="1"/>
+    <col min="4" max="4" width="12.0952380952381" customWidth="1"/>
+    <col min="5" max="5" width="14.5428571428571" customWidth="1"/>
+    <col min="6" max="6" width="17.6380952380952" customWidth="1"/>
+    <col min="7" max="7" width="20.0952380952381" customWidth="1"/>
+    <col min="8" max="8" width="16.0952380952381" customWidth="1"/>
+    <col min="9" max="9" width="22.6380952380952" customWidth="1"/>
+    <col min="10" max="10" width="15.3619047619048" customWidth="1"/>
+    <col min="11" max="11" width="21.9047619047619" customWidth="1"/>
+    <col min="12" max="12" width="18.7238095238095" customWidth="1"/>
+    <col min="13" max="13" width="16.2761904761905" customWidth="1"/>
+    <col min="14" max="14" width="17.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:14">
+    <row r="1" s="7" customFormat="1" spans="1:15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1207,11 +1211,14 @@
       </c>
       <c r="N1" s="7" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>66</v>
@@ -1223,12 +1230,12 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1237,7 +1244,7 @@
         <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>55</v>
@@ -1256,12 +1263,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="D11:H20"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="4" max="4" width="22.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="34.9090909090909" customWidth="1"/>
+    <col min="4" max="4" width="22.6380952380952" customWidth="1"/>
+    <col min="5" max="5" width="34.9047619047619" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="16.4545454545455" customWidth="1"/>
+    <col min="7" max="7" width="16.4571428571429" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1274,7 +1281,7 @@
     </row>
     <row r="12" ht="21" spans="4:8">
       <c r="D12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -1283,16 +1290,16 @@
     </row>
     <row r="13" spans="4:8">
       <c r="D13" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H13" s="3"/>
     </row>
@@ -1301,13 +1308,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="4:7">
@@ -1315,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="16" spans="4:7">
@@ -1329,13 +1336,13 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="4:7">
@@ -1343,13 +1350,13 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="4:7">
@@ -1357,13 +1364,13 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="4:7">
@@ -1371,13 +1378,13 @@
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="4:7">
@@ -1385,13 +1392,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Source/SmartInventory/SmartInventory/Content/Templates/Bulk/FiberData.xlsx
+++ b/Source/SmartInventory/SmartInventory/Content/Templates/Bulk/FiberData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19035" windowHeight="7620"/>
+    <workbookView windowWidth="19635" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,63 +28,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
-  <si>
-    <t>link_type</t>
-  </si>
-  <si>
-    <t>link_id</t>
-  </si>
-  <si>
-    <t>link_name</t>
-  </si>
-  <si>
-    <t>main_link_id</t>
-  </si>
-  <si>
-    <t>main_link_type</t>
-  </si>
-  <si>
-    <t>redundant_link_id</t>
-  </si>
-  <si>
-    <t>redundant_link_type</t>
-  </si>
-  <si>
-    <t>start_point_type</t>
-  </si>
-  <si>
-    <t>start_point_network_id</t>
-  </si>
-  <si>
-    <t>start_point_location</t>
-  </si>
-  <si>
-    <t>end_point_type</t>
-  </si>
-  <si>
-    <t>end_point_network_id</t>
-  </si>
-  <si>
-    <t>end_point_location</t>
-  </si>
-  <si>
-    <t>each_lmc_length</t>
-  </si>
-  <si>
-    <t>link_prefix</t>
-  </si>
-  <si>
-    <t>Main Link</t>
-  </si>
-  <si>
-    <t>Optical</t>
-  </si>
-  <si>
-    <t>Rudandant Link</t>
-  </si>
-  <si>
-    <t>MU</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+  <si>
+    <t>Link Prefix</t>
+  </si>
+  <si>
+    <t>Link Type</t>
+  </si>
+  <si>
+    <t>OP_ALIAS</t>
+  </si>
+  <si>
+    <t>Main_link_id</t>
+  </si>
+  <si>
+    <t>CX</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>TX000000000000</t>
   </si>
   <si>
     <t>GUIDELINE FOR FILLING FIBER DETAILS</t>
@@ -96,13 +63,19 @@
     <t>Description</t>
   </si>
   <si>
+    <t>value</t>
+  </si>
+  <si>
     <t>Data Type</t>
   </si>
   <si>
     <t>IS Nullable/Blank</t>
   </si>
   <si>
-    <t>link_type Can Not Be Blank!</t>
+    <t>Link Prefix  Can Not Be Blank!</t>
+  </si>
+  <si>
+    <t>TX,CX,IP,GPON</t>
   </si>
   <si>
     <t>varchar</t>
@@ -111,19 +84,16 @@
     <t>No</t>
   </si>
   <si>
-    <t>link_id Can Not Be Blank!</t>
-  </si>
-  <si>
-    <t>link_name Can Not Be Blank!</t>
-  </si>
-  <si>
-    <t>main_link_id Can Not Be Blank!</t>
-  </si>
-  <si>
-    <t>main_link_type Can Not Be Blank!</t>
-  </si>
-  <si>
-    <t>redundant_link_id Can Not Be Blank!</t>
+    <t xml:space="preserve">Link Type </t>
+  </si>
+  <si>
+    <t>Link Type  Can Not Be Blank!</t>
+  </si>
+  <si>
+    <t>Spur Link,Main Link,Radundant Link</t>
+  </si>
+  <si>
+    <t>optional</t>
   </si>
 </sst>
 </file>
@@ -136,7 +106,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,12 +137,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Courier New"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -317,7 +281,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,12 +303,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,52 +634,55 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -733,76 +694,73 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -817,20 +775,18 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,6 +846,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1150,108 +1113,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15"/>
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="9.27619047619048" customWidth="1"/>
-    <col min="3" max="3" width="15.5428571428571" customWidth="1"/>
-    <col min="4" max="4" width="12.0952380952381" customWidth="1"/>
-    <col min="5" max="5" width="14.5428571428571" customWidth="1"/>
-    <col min="6" max="6" width="17.6380952380952" customWidth="1"/>
-    <col min="7" max="7" width="20.0952380952381" customWidth="1"/>
-    <col min="8" max="8" width="16.0952380952381" customWidth="1"/>
-    <col min="9" max="9" width="22.6380952380952" customWidth="1"/>
-    <col min="10" max="10" width="15.3619047619048" customWidth="1"/>
-    <col min="11" max="11" width="21.9047619047619" customWidth="1"/>
-    <col min="12" max="12" width="18.7238095238095" customWidth="1"/>
-    <col min="13" max="13" width="16.2761904761905" customWidth="1"/>
-    <col min="14" max="14" width="17.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="12.0952380952381" customWidth="1"/>
+    <col min="4" max="4" width="14.5428571428571" customWidth="1"/>
+    <col min="5" max="5" width="17.6380952380952" customWidth="1"/>
+    <col min="6" max="6" width="20.0952380952381" customWidth="1"/>
+    <col min="7" max="7" width="16.0952380952381" customWidth="1"/>
+    <col min="8" max="8" width="22.6380952380952" customWidth="1"/>
+    <col min="9" max="9" width="15.3619047619048" customWidth="1"/>
+    <col min="10" max="10" width="21.9047619047619" customWidth="1"/>
+    <col min="11" max="11" width="18.7238095238095" customWidth="1"/>
+    <col min="12" max="12" width="16.2761904761905" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:15">
-      <c r="A1" s="8" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:21">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2">
-        <v>66</v>
-      </c>
-      <c r="C2">
-        <v>123</v>
-      </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>65</v>
-      </c>
-      <c r="C3">
-        <v>57</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="3:3">
-      <c r="C14" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1262,149 +1184,103 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="D11:H20"/>
-  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15" outlineLevelCol="7"/>
+  <dimension ref="D1:I6"/>
+  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="4" max="4" width="22.6380952380952" customWidth="1"/>
-    <col min="5" max="5" width="34.9047619047619" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="16.4571428571429" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="5" max="6" width="34.9047619047619" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="16.4571428571429" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="4:8">
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+    <row r="1" spans="4:9">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
-    <row r="12" ht="21" spans="4:8">
-      <c r="D12" s="2" t="s">
+    <row r="2" ht="21" spans="4:9">
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="4:9">
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="4:8">
+      <c r="D4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="4:8">
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="F5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="13" spans="4:8">
-      <c r="D13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="3" t="s">
+    <row r="6" spans="4:8">
+      <c r="D6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="4:7">
-      <c r="D14" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="4:7">
-      <c r="D15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="4:7">
-      <c r="D16" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="4:7">
-      <c r="D17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7">
-      <c r="D18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="4:7">
-      <c r="D19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="4:7">
-      <c r="D20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
